--- a/assembly-bom (2).xlsx
+++ b/assembly-bom (2).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hclo365-my.sharepoint.com/personal/manasabhay_orpe_hcltech_com/Documents/Documents/GitHub/template/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="11_7135ECC0D47B8AE3ED9B64D3525ED87656CD4A6F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F0EE427-681B-4DE1-98E5-1DBA0C4954B1}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="11_7135ECC0D47B8AE3ED9B64D3525ED87656CD4A6F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EC0622DC-0612-4AF6-9F6A-2D8AD111996E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,9 +37,6 @@
     <t>Standards</t>
   </si>
   <si>
-    <t>123</t>
-  </si>
-  <si>
     <t>Part Number</t>
   </si>
   <si>
@@ -119,6 +116,9 @@
   </si>
   <si>
     <t>Black circular metal washer/spacer with central bore, visible chamfered/stepped outer profile</t>
+  </si>
+  <si>
+    <t>ps:234</t>
   </si>
 </sst>
 </file>
@@ -510,56 +510,56 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="I5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="J5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="K5" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="B6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="E6">
         <v>1060</v>
@@ -574,10 +574,10 @@
         <v>4243.71</v>
       </c>
       <c r="I6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J6" t="s">
         <v>19</v>
-      </c>
-      <c r="J6" t="s">
-        <v>20</v>
       </c>
       <c r="K6">
         <v>7.85</v>
@@ -585,13 +585,13 @@
     </row>
     <row r="7" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="E7">
         <v>42</v>
@@ -606,10 +606,10 @@
         <v>110.78</v>
       </c>
       <c r="I7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J7" t="s">
         <v>19</v>
-      </c>
-      <c r="J7" t="s">
-        <v>20</v>
       </c>
       <c r="K7">
         <v>7.85</v>
@@ -617,16 +617,16 @@
     </row>
     <row r="8" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E8">
         <v>560</v>
@@ -641,10 +641,10 @@
         <v>9671.2000000000007</v>
       </c>
       <c r="I8" t="s">
+        <v>18</v>
+      </c>
+      <c r="J8" t="s">
         <v>19</v>
-      </c>
-      <c r="J8" t="s">
-        <v>20</v>
       </c>
       <c r="K8">
         <v>7.85</v>
@@ -652,16 +652,16 @@
     </row>
     <row r="9" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C9">
         <v>1</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E9">
         <v>31</v>
@@ -676,10 +676,10 @@
         <v>67.89</v>
       </c>
       <c r="I9" t="s">
+        <v>18</v>
+      </c>
+      <c r="J9" t="s">
         <v>19</v>
-      </c>
-      <c r="J9" t="s">
-        <v>20</v>
       </c>
       <c r="K9">
         <v>7.85</v>
@@ -687,16 +687,16 @@
     </row>
     <row r="10" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" t="s">
         <v>25</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="E10">
         <v>196</v>
@@ -711,10 +711,10 @@
         <v>31947.49</v>
       </c>
       <c r="I10" t="s">
+        <v>18</v>
+      </c>
+      <c r="J10" t="s">
         <v>19</v>
-      </c>
-      <c r="J10" t="s">
-        <v>20</v>
       </c>
       <c r="K10">
         <v>7.85</v>
@@ -722,16 +722,16 @@
     </row>
     <row r="11" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11">
         <v>1</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E11">
         <v>720</v>
@@ -746,10 +746,10 @@
         <v>1681.47</v>
       </c>
       <c r="I11" t="s">
+        <v>18</v>
+      </c>
+      <c r="J11" t="s">
         <v>19</v>
-      </c>
-      <c r="J11" t="s">
-        <v>20</v>
       </c>
       <c r="K11">
         <v>7.85</v>
@@ -757,13 +757,13 @@
     </row>
     <row r="12" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C12">
         <v>1</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E12">
         <v>1820</v>
@@ -778,10 +778,10 @@
         <v>147513.26999999999</v>
       </c>
       <c r="I12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J12" t="s">
         <v>19</v>
-      </c>
-      <c r="J12" t="s">
-        <v>20</v>
       </c>
       <c r="K12">
         <v>7.85</v>
@@ -789,16 +789,16 @@
     </row>
     <row r="13" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C13">
         <v>1</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E13">
         <v>760</v>
@@ -813,10 +813,10 @@
         <v>2744.36</v>
       </c>
       <c r="I13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J13" t="s">
         <v>19</v>
-      </c>
-      <c r="J13" t="s">
-        <v>20</v>
       </c>
       <c r="K13">
         <v>7.85</v>
@@ -824,16 +824,16 @@
     </row>
     <row r="14" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" t="s">
         <v>25</v>
       </c>
-      <c r="B14" t="s">
-        <v>26</v>
-      </c>
       <c r="C14">
         <v>1</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E14">
         <v>150</v>
@@ -848,10 +848,10 @@
         <v>19428.75</v>
       </c>
       <c r="I14" t="s">
+        <v>18</v>
+      </c>
+      <c r="J14" t="s">
         <v>19</v>
-      </c>
-      <c r="J14" t="s">
-        <v>20</v>
       </c>
       <c r="K14">
         <v>7.85</v>
@@ -859,16 +859,16 @@
     </row>
     <row r="15" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C15">
         <v>1</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E15">
         <v>58</v>
@@ -883,10 +883,10 @@
         <v>290.48</v>
       </c>
       <c r="I15" t="s">
+        <v>18</v>
+      </c>
+      <c r="J15" t="s">
         <v>19</v>
-      </c>
-      <c r="J15" t="s">
-        <v>20</v>
       </c>
       <c r="K15">
         <v>7.85</v>
